--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>423243.8877901005</v>
+        <v>423244</v>
       </c>
       <c r="R2" t="n">
-        <v>6200062.661815801</v>
+        <v>6200063</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2000-06-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98918</v>
+        <v>98921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98921</v>
+        <v>98925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98925</v>
+        <v>98926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98926</v>
+        <v>98953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98953</v>
+        <v>98959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98959</v>
+        <v>98966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98966</v>
+        <v>98970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98970</v>
+        <v>98977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98980</v>
+        <v>98985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98985</v>
+        <v>98993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21568-2021 artfynd.xlsx
+++ b/artfynd/A 21568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63555835</v>
       </c>
       <c r="B2" t="n">
-        <v>98993</v>
+        <v>99003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
